--- a/public/tripsfactory-turlar-shabloni.xlsx
+++ b/public/tripsfactory-turlar-shabloni.xlsx
@@ -225,12 +225,14 @@
           <rPr>
             <sz val="10"/>
           </rPr>
-          <t xml:space="preserve">Har bir kun alohida qatorda, «1-kun.» bilan boshlanadi.
+          <t xml:space="preserve">Har bir kun «1-kun.» bilan boshlanadi. Kun sarlavhasi — birinchi qatorda, tavsif — keyingi qatorda.
 FORMAT:
-1-kun. Arrival in Tashkent — Meet at the airport and transfer to the hotel.
-2-kun. Tashkent city tour — Khast-Imam, Chorsu Bazaar and the metro.
-MUHIM: sarlavha bilan tavsif orasiga « — » qo'ying. Qo'ymasangiz butun matn tavsifga tushadi, sarlavha esa «Day 1» bo'ladi.
-Katak ichida yangi qator: Ctrl+Enter (Mac'da Cmd+Enter).</t>
+1-kun. Arrival in Tashkent
+Meet at the airport and transfer to the hotel.
+2-kun. Tashkent city tour
+Khast-Imam, Chorsu Bazaar and the metro.
+Katak ichida yangi qator: Ctrl+Enter (Mac'da Cmd+Enter).
+Sarlavha bilan tavsifni bitta qatorga yozsangiz, sayt sarlavhasi «Day 1», «Day 2» bo'ladi — matn to'liq saqlanadi, faqat sarlavha chiroyliroq bo'lmaydi.</t>
         </r>
       </text>
     </comment>
@@ -530,14 +532,22 @@
     <t>Our most popular escorted tour: the ancient cities of Khiva, Bukhara and Samarkand plus the modern capital Tashkent, in one seamless 8-day journey with guaranteed departures.</t>
   </si>
   <si>
-    <t xml:space="preserve">1-kun. Arrival in Tashkent — Meet at the airport, transfer to your hotel and rest. In the evening, an optional welcome walk along Amir Timur Square.
-2-kun. Tashkent city tour — Khast-Imam Complex with the 7th-century Ottoman Quran, Chorsu Bazaar, the Museum of Applied Arts and the famously ornate metro stations.
-3-kun. Fly to Urgench — Khiva — Morning flight and full-day walking tour of Itchan Kala: Kalta Minor, Kunya-Ark, Tash Hauli Palace and sunset from the city walls.
-4-kun. Khiva → Bukhara — Cross the Kyzylkum desert along the Amu Darya river. Evening arrival in Bukhara, dinner in a former madrasah courtyard.
-5-kun. Bukhara old town — Poi-Kalyan ensemble, Ark Fortress, trading domes and Lyabi-Hauz, finishing with a folklore show in the Nodir Devon Begi madrasah.
-6-kun. Bukhara → Samarkand — Drive to Samarkand with a stop at the Sitorai Mokhi-Khosa summer palace. Afternoon visit to Gur-e-Amir, Tamerlane's mausoleum.
-7-kun. Samarkand highlights — Registan Square, Bibi-Khanym Mosque, the Shah-i-Zinda necropolis and the Siab Bazaar; evening high-speed Afrosiyob train to Tashkent.
-8-kun. Departure — Transfer to Tashkent airport for your flight home.</t>
+    <t xml:space="preserve">1-kun. Arrival in Tashkent
+Meet at the airport, transfer to your hotel and rest. In the evening, an optional welcome walk along Amir Timur Square.
+2-kun. Tashkent city tour
+Khast-Imam Complex with the 7th-century Ottoman Quran, Chorsu Bazaar, the Museum of Applied Arts and the famously ornate metro stations.
+3-kun. Fly to Urgench — Khiva
+Morning flight and full-day walking tour of Itchan Kala: Kalta Minor, Kunya-Ark, Tash Hauli Palace and sunset from the city walls.
+4-kun. Khiva → Bukhara
+Cross the Kyzylkum desert along the Amu Darya river. Evening arrival in Bukhara, dinner in a former madrasah courtyard.
+5-kun. Bukhara old town
+Poi-Kalyan ensemble, Ark Fortress, trading domes and Lyabi-Hauz, finishing with a folklore show in the Nodir Devon Begi madrasah.
+6-kun. Bukhara → Samarkand
+Drive to Samarkand with a stop at the Sitorai Mokhi-Khosa summer palace. Afternoon visit to Gur-e-Amir, Tamerlane's mausoleum.
+7-kun. Samarkand highlights
+Registan Square, Bibi-Khanym Mosque, the Shah-i-Zinda necropolis and the Siab Bazaar; evening high-speed Afrosiyob train to Tashkent.
+8-kun. Departure
+Transfer to Tashkent airport for your flight home.</t>
   </si>
   <si>
     <t xml:space="preserve">7 nights in double room with breakfast
@@ -600,17 +610,28 @@
     <t>An 11-day winter journey from Beijing across Manchuria to Harbin's famous Ice and Snow Festival — the Great Wall at Simatai, imperial Chengde, Shenyang and Jilin, the snow forests of Xuegu and the ice city of Harbin. Small-group tour with a Russian-speaking guide; price per person depends on group size (from about $1,916 for 16 travellers to $4,028 for two).</t>
   </si>
   <si>
-    <t xml:space="preserve">1-kun. Arrival in Beijing — Gubei — Airport pickup in Beijing and transfer to Gubei. Check in to a hot-spring hotel, stroll through the ancient Gubei Water Town and visit the Simatai section of the Great Wall. Relax in the hotel's thermal springs in the evening.
-2-kun. Gubei — Beijing — Morning walk in Gubei Water Town, then transfer back to Beijing. Visit Shichahai park and go ice-skating on the frozen lake. Check in to a hotel in central Beijing.
-3-kun. Beijing — Explore the Forbidden City and Jingshan park, enjoy a traditional tea ceremony, wander Beijing's old hutongs and end the day with a classic Peking duck dinner.
-4-kun. Beijing — Chengde — High-speed train to Chengde (1 hour). Tour the Qing emperors' Summer Resort and visit the Putuo Zongcheng and Puning temples. Overnight at a hot-spring hotel.
-5-kun. Chengde — Shenyang — High-speed train to Shenyang (3 hours). Visit the Mukden Imperial Palace and the old town, with free time to explore the city.
-6-kun. Shenyang — Jilin — High-speed train to Jilin (2.5 hours). Visit Beishan park, the Lanyue pavilion and Taoist temples, and stroll along the Songhua river embankment.
-7-kun. Jilin — Snow Valley (Xuegu) — Early morning: watch the famous winter rime frost along the Songjiang embankment. Then transfer to Snow Valley (Xuegu, 4 hours) — a magical snow-covered forest village.
-8-kun. Snow Valley (Xuegu) — A full day in Snow Valley: walks through the snow-blanketed landscape and free time. Optional winter activities — tubing, snowmobiles, horse rides, sledding and a winter photo session.
-9-kun. Snow Valley — Harbin — Transfer to Harbin (4 hours). Visit the world-famous International Ice and Snow Festival and enjoy a Harbin-cuisine dinner.
-10-kun. Harbin — Harbin city tour: the old railway station, Russian Harbin, the city history museum and Central Street, finishing with the glowing ice lights of Harbin.
-11-kun. Harbin — Departure — Transfer to the airport for your flight home, or onward to Beijing.</t>
+    <t xml:space="preserve">1-kun. Arrival in Beijing — Gubei
+Airport pickup in Beijing and transfer to Gubei. Check in to a hot-spring hotel, stroll through the ancient Gubei Water Town and visit the Simatai section of the Great Wall. Relax in the hotel's thermal springs in the evening.
+2-kun. Gubei — Beijing
+Morning walk in Gubei Water Town, then transfer back to Beijing. Visit Shichahai park and go ice-skating on the frozen lake. Check in to a hotel in central Beijing.
+3-kun. Beijing
+Explore the Forbidden City and Jingshan park, enjoy a traditional tea ceremony, wander Beijing's old hutongs and end the day with a classic Peking duck dinner.
+4-kun. Beijing — Chengde
+High-speed train to Chengde (1 hour). Tour the Qing emperors' Summer Resort and visit the Putuo Zongcheng and Puning temples. Overnight at a hot-spring hotel.
+5-kun. Chengde — Shenyang
+High-speed train to Shenyang (3 hours). Visit the Mukden Imperial Palace and the old town, with free time to explore the city.
+6-kun. Shenyang — Jilin
+High-speed train to Jilin (2.5 hours). Visit Beishan park, the Lanyue pavilion and Taoist temples, and stroll along the Songhua river embankment.
+7-kun. Jilin — Snow Valley (Xuegu)
+Early morning: watch the famous winter rime frost along the Songjiang embankment. Then transfer to Snow Valley (Xuegu, 4 hours) — a magical snow-covered forest village.
+8-kun. Snow Valley (Xuegu)
+A full day in Snow Valley: walks through the snow-blanketed landscape and free time. Optional winter activities — tubing, snowmobiles, horse rides, sledding and a winter photo session.
+9-kun. Snow Valley — Harbin
+Transfer to Harbin (4 hours). Visit the world-famous International Ice and Snow Festival and enjoy a Harbin-cuisine dinner.
+10-kun. Harbin
+Harbin city tour: the old railway station, Russian Harbin, the city history museum and Central Street, finishing with the glowing ice lights of Harbin.
+11-kun. Harbin — Departure
+Transfer to the airport for your flight home, or onward to Beijing.</t>
   </si>
   <si>
     <t xml:space="preserve">10 nights in 4–5★ hotels, standard twin/double rooms
@@ -1350,7 +1371,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="6" ht="284" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" ht="419" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>35</v>
       </c>
@@ -1409,7 +1430,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="7" ht="459.5" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" ht="689" customHeight="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>53</v>
       </c>
